--- a/pasto_case/results/AHP_results/AHP_TOPSIS_results4.xlsx
+++ b/pasto_case/results/AHP_results/AHP_TOPSIS_results4.xlsx
@@ -478,249 +478,249 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ICEV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0279551329238573</v>
+        <v>0.02796553430629584</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02685648551874553</v>
+        <v>0.02680941426443351</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008263997303411609</v>
+        <v>0.007555129158571264</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009067547232928006</v>
+        <v>0.0003531880973599173</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001432231292055224</v>
+        <v>0.002717590909696779</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09438378464933082</v>
+        <v>0.0851949384330714</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01787202688913055</v>
+        <v>0.01774738154912828</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1592080324768503</v>
+        <v>0.1724012199472198</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EVL1</t>
+          <t>EV-L1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01100296250130439</v>
+        <v>0.01090775991096021</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02451182752506119</v>
+        <v>0.0243514742112309</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02302744424505471</v>
+        <v>0.02763863473494008</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03850400103739018</v>
+        <v>0.03464880719993516</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02851218724031516</v>
+        <v>0.03909518674566557</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06717196422470277</v>
+        <v>0.05186265923413805</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04874245002002184</v>
+        <v>0.05393353110276028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4205037858114368</v>
+        <v>0.5097870814725357</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EVL2</t>
+          <t>EV-L2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02678606471377718</v>
+        <v>0.02677813472391658</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02451182752506119</v>
+        <v>0.0243514742112309</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02302744424505471</v>
+        <v>0.02763863473494008</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03850400103739018</v>
+        <v>0.03464880719993516</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02851218724031516</v>
+        <v>0.03909518674566557</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06499727359150766</v>
+        <v>0.04897677329122787</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05123409752697602</v>
+        <v>0.05622005490851223</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4407940561481385</v>
+        <v>0.5344272814173224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EVL3</t>
+          <t>EV-L3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02757263452482788</v>
+        <v>0.02760731693243346</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02451182752506119</v>
+        <v>0.0243514742112309</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02228622872761524</v>
+        <v>0.02622714149818373</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03850400103739018</v>
+        <v>0.03464880719993516</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02851218724031516</v>
+        <v>0.03909518674566557</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06572277178833946</v>
+        <v>0.05037262907116116</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05127420475674564</v>
+        <v>0.05597318849681917</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4382523913939518</v>
+        <v>0.52633182739922</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CNG</t>
+          <t>NGV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02522483904268785</v>
+        <v>0.02527654641803782</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02119669196327659</v>
+        <v>0.02191024244379168</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08750183113142575</v>
+        <v>0.07653814496408005</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01030991949221462</v>
+        <v>0.01747236425009188</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004116226354827212</v>
+        <v>0.005821664841475563</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04325226032041342</v>
+        <v>0.03786341686915735</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0810957423005845</v>
+        <v>0.07257974898297229</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6521676310938214</v>
+        <v>0.6571683129778081</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>PHEVL1</t>
+          <t>PHEV-L1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02553941519874944</v>
+        <v>0.02552660070069192</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02613711331426478</v>
+        <v>0.02607530688602737</v>
       </c>
       <c r="D7" t="n">
-        <v>0.011964351449146</v>
+        <v>0.01146743830309493</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02442377422410735</v>
+        <v>0.02607600868424756</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03630499354405736</v>
+        <v>0.02472506133727698</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07688131008761913</v>
+        <v>0.06723766057809168</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04492848310638329</v>
+        <v>0.03731429597690209</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3688413051882223</v>
+        <v>0.3568971562696196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>PHEVL2</t>
+          <t>PHEV-L2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02791890171849144</v>
+        <v>0.02792678451806492</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02613711331426478</v>
+        <v>0.02607530688602737</v>
       </c>
       <c r="D8" t="n">
-        <v>0.011964351449146</v>
+        <v>0.01146743830309493</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02442377422410735</v>
+        <v>0.02607600868424756</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03630499354405736</v>
+        <v>0.02472506133727698</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07684196578156537</v>
+        <v>0.06719178747670748</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04575378822365507</v>
+        <v>0.03831831646606572</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3732085878088955</v>
+        <v>0.3631720094489613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>PHEVL3</t>
+          <t>PHEV-L3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02800004937630452</v>
+        <v>0.02801132248959926</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02613711331426478</v>
+        <v>0.02607530688602737</v>
       </c>
       <c r="D9" t="n">
-        <v>0.011964351449146</v>
+        <v>0.01146743830309493</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02442377422410735</v>
+        <v>0.02607600868424756</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03630499354405736</v>
+        <v>0.02472506133727698</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07684192293424791</v>
+        <v>0.06719173429556938</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04578385195078951</v>
+        <v>0.03835593866792664</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3733623864453636</v>
+        <v>0.3633991881677217</v>
       </c>
     </row>
   </sheetData>
